--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -7,14 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from Key Population S" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from Key Population S" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,58 +99,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>472986005</t>
-  </si>
-  <si>
-    <t>Sexually active with men</t>
-  </si>
-  <si>
-    <t>159799000</t>
-  </si>
-  <si>
-    <t>Female prostitute</t>
-  </si>
-  <si>
-    <t>159800001</t>
-  </si>
-  <si>
-    <t>Male prostitute</t>
-  </si>
-  <si>
-    <t>228388006</t>
-  </si>
-  <si>
-    <t>Intravenous drug user</t>
-  </si>
-  <si>
-    <t>417284009</t>
-  </si>
-  <si>
-    <t>Current drug user</t>
-  </si>
-  <si>
-    <t>407375002</t>
-  </si>
-  <si>
-    <t>Surgically transgendered transsexual</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
     <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
   </si>
   <si>
     <t>http://openhie.org/fhir/rwanda-hiv/CodeSystem/cs-key-population-status</t>
@@ -418,7 +375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -429,112 +386,26 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from Key Population S" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from Key Population S" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,16 +100,58 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>472986005</t>
+  </si>
+  <si>
+    <t>Sexually active with men</t>
+  </si>
+  <si>
+    <t>159799000</t>
+  </si>
+  <si>
+    <t>Female prostitute</t>
+  </si>
+  <si>
+    <t>159800001</t>
+  </si>
+  <si>
+    <t>Male prostitute</t>
+  </si>
+  <si>
+    <t>228388006</t>
+  </si>
+  <si>
+    <t>Intravenous drug user</t>
+  </si>
+  <si>
+    <t>417284009</t>
+  </si>
+  <si>
+    <t>Current drug user</t>
+  </si>
+  <si>
+    <t>407375002</t>
+  </si>
+  <si>
+    <t>Surgically transgendered transsexual</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>Codes</t>
   </si>
   <si>
     <t>All codes</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
   </si>
   <si>
     <t>http://openhie.org/fhir/rwanda-hiv/CodeSystem/cs-key-population-status</t>
@@ -375,6 +418,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -384,28 +513,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T17:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-key-population-status.xlsx
+++ b/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
